--- a/111/111_111/005_AES2/条件输入数据表.xlsx
+++ b/111/111_111/005_AES2/条件输入数据表.xlsx
@@ -1128,8 +1128,16 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D2" s="35" t="inlineStr"/>
-      <c r="E2" s="16" t="inlineStr"/>
+      <c r="D2" s="35" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
       <c r="G2" s="41" t="n"/>
       <c r="H2" s="41" t="n"/>
       <c r="I2" s="5" t="inlineStr">
@@ -1838,9 +1846,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="K1:L1"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
